--- a/PlainWallet/Doc/Logo_converter.xlsx
+++ b/PlainWallet/Doc/Logo_converter.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositories\MAUI\PlainWallet\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01DD9796-8670-49AC-99E3-588A2CA48982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89357F21-6AAC-41FF-8FB4-9DC8BCF41C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57615" yWindow="9540" windowWidth="28770" windowHeight="14970" xr2:uid="{7A7FB264-F2D1-4759-BE78-6B916B9FFC5F}"/>
+    <workbookView xWindow="57615" yWindow="9540" windowWidth="28770" windowHeight="14970" activeTab="1" xr2:uid="{7A7FB264-F2D1-4759-BE78-6B916B9FFC5F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="46">
   <si>
     <t>Filename</t>
   </si>
@@ -120,6 +121,60 @@
   </si>
   <si>
     <t>#FF00FF00</t>
+  </si>
+  <si>
+    <t>cleveland_botanical_garden.svg</t>
+  </si>
+  <si>
+    <t>cleveland_metroparks_zoo.svg</t>
+  </si>
+  <si>
+    <t>cma_cleveland_museum_of_art.svg</t>
+  </si>
+  <si>
+    <t>columbus_zoo.svg</t>
+  </si>
+  <si>
+    <t>cuyahoga_county_public_library.svg</t>
+  </si>
+  <si>
+    <t>holden_arboretum.svg</t>
+  </si>
+  <si>
+    <t>lake_metroparks.svg</t>
+  </si>
+  <si>
+    <t>museum_of_natural_history_cleveland.svg</t>
+  </si>
+  <si>
+    <t>shaker_library.svg</t>
+  </si>
+  <si>
+    <t>vitamin_shoppe.svg</t>
+  </si>
+  <si>
+    <t>#cc0000ff</t>
+  </si>
+  <si>
+    <t>#1482c2ff</t>
+  </si>
+  <si>
+    <t>#006554ff</t>
+  </si>
+  <si>
+    <t>#2360a5ff</t>
+  </si>
+  <si>
+    <t>#ed1c24ff</t>
+  </si>
+  <si>
+    <t>#ff0000ff</t>
+  </si>
+  <si>
+    <t>#1e71b8ff</t>
+  </si>
+  <si>
+    <t>#606b21ff</t>
   </si>
 </sst>
 </file>
@@ -737,4 +792,365 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12AF9107-BAA4-4C14-851E-431B817A19B0}">
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="str">
+        <f>"new LogoInfo("""&amp;A2&amp;""","""&amp;B2&amp;"""), "</f>
+        <v xml:space="preserve">new LogoInfo("ace_hardware.svg",""), </v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F37" si="0">"new LogoInfo("""&amp;A3&amp;""","""&amp;B3&amp;"""), "</f>
+        <v xml:space="preserve">new LogoInfo("barnes_noble.svg",""), </v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("big_lots.svg",""), </v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("cleveland_botanical_garden.svg",""), </v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("cleveland_metroparks_zoo.svg",""), </v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("cma_cleveland_museum_of_art.svg",""), </v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("columbus_zoo.svg",""), </v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("costco_wholesale.svg",""), </v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("cuyahoga_county_public_library.svg",""), </v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("cvs.svg","#cc0000ff"), </v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("decathlon.svg","#1482c2ff"), </v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("dicks_sporting_goods.svg","#006554ff"), </v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("dm.svg",""), </v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("giant_eagle.svg",""), </v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("heinens.svg",""), </v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("holden_arboretum.svg",""), </v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("ikea.svg","#2360a5ff"), </v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("lake_metroparks.svg",""), </v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("lakeshore_learning.svg","#ed1c24ff"), </v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("lego.svg","#ff0000ff"), </v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F22" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("lidl.svg","#1e71b8ff"), </v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("lowe_s.svg",""), </v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("moma.svg",""), </v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("museum_of_natural_history_cleveland.svg",""), </v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("ollie_s.svg",""), </v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("panera_bread.svg","#606b21ff"), </v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("pet_supplies_plus.svg",""), </v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("petsmart.svg",""), </v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>36</v>
+      </c>
+      <c r="F30" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("shaker_library.svg",""), </v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("target.svg",""), </v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("tesco.svg",""), </v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F33" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("vitamin_shoppe.svg",""), </v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("walgreens.svg",""), </v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("walmart.svg",""), </v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>26</v>
+      </c>
+      <c r="F36" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("whole_foods.svg",""), </v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/PlainWallet/Doc/Logo_converter.xlsx
+++ b/PlainWallet/Doc/Logo_converter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositories\MAUI\PlainWallet\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89357F21-6AAC-41FF-8FB4-9DC8BCF41C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61422297-0A58-4BA0-A82C-C1D5ED0827F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57615" yWindow="9540" windowWidth="28770" windowHeight="14970" activeTab="1" xr2:uid="{7A7FB264-F2D1-4759-BE78-6B916B9FFC5F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="68">
   <si>
     <t>Filename</t>
   </si>
@@ -175,6 +175,72 @@
   </si>
   <si>
     <t>#606b21ff</t>
+  </si>
+  <si>
+    <t>banana_republic.svg</t>
+  </si>
+  <si>
+    <t>Best_Buy.svg</t>
+  </si>
+  <si>
+    <t>Home_Depot.svg</t>
+  </si>
+  <si>
+    <t>H_M.svg</t>
+  </si>
+  <si>
+    <t>Gap.svg</t>
+  </si>
+  <si>
+    <t>Old_Navy.svg</t>
+  </si>
+  <si>
+    <t>rei.svg</t>
+  </si>
+  <si>
+    <t>columbia.svg</t>
+  </si>
+  <si>
+    <t>skechers.svg</t>
+  </si>
+  <si>
+    <t>under_armour.svg</t>
+  </si>
+  <si>
+    <t>adidas.svg</t>
+  </si>
+  <si>
+    <t>nike.svg</t>
+  </si>
+  <si>
+    <t>foot_locker.svg</t>
+  </si>
+  <si>
+    <t>jcpenney.svg</t>
+  </si>
+  <si>
+    <t>kohl_s.svg</t>
+  </si>
+  <si>
+    <t>dillard_s.svg</t>
+  </si>
+  <si>
+    <t>carter_s.svg</t>
+  </si>
+  <si>
+    <t>pampers.svg</t>
+  </si>
+  <si>
+    <t>macy_s.svg</t>
+  </si>
+  <si>
+    <t>#008061ff</t>
+  </si>
+  <si>
+    <t>#f96302ff</t>
+  </si>
+  <si>
+    <t>seven_7_eleven.svg</t>
   </si>
 </sst>
 </file>
@@ -796,7 +862,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12AF9107-BAA4-4C14-851E-431B817A19B0}">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
@@ -824,7 +890,7 @@
         <v>3</v>
       </c>
       <c r="F3" t="str">
-        <f t="shared" ref="F3:F37" si="0">"new LogoInfo("""&amp;A3&amp;""","""&amp;B3&amp;"""), "</f>
+        <f t="shared" ref="F3:F56" si="0">"new LogoInfo("""&amp;A3&amp;""","""&amp;B3&amp;"""), "</f>
         <v xml:space="preserve">new LogoInfo("barnes_noble.svg",""), </v>
       </c>
     </row>
@@ -1147,6 +1213,192 @@
       <c r="F36" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">new LogoInfo("whole_foods.svg",""), </v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F37" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("banana_republic.svg",""), </v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>47</v>
+      </c>
+      <c r="F38" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("Best_Buy.svg",""), </v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" t="s">
+        <v>66</v>
+      </c>
+      <c r="F39" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("Home_Depot.svg","#f96302ff"), </v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>67</v>
+      </c>
+      <c r="B40" t="s">
+        <v>65</v>
+      </c>
+      <c r="F40" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("seven_7_eleven.svg","#008061ff"), </v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>49</v>
+      </c>
+      <c r="F41" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("H_M.svg",""), </v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>50</v>
+      </c>
+      <c r="F42" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("Gap.svg",""), </v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>51</v>
+      </c>
+      <c r="F43" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("Old_Navy.svg",""), </v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>52</v>
+      </c>
+      <c r="F44" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("rei.svg",""), </v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>53</v>
+      </c>
+      <c r="F45" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("columbia.svg",""), </v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>54</v>
+      </c>
+      <c r="F46" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("skechers.svg",""), </v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>55</v>
+      </c>
+      <c r="F47" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("under_armour.svg",""), </v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>56</v>
+      </c>
+      <c r="F48" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("adidas.svg",""), </v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>57</v>
+      </c>
+      <c r="F49" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("nike.svg",""), </v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>58</v>
+      </c>
+      <c r="F50" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("foot_locker.svg",""), </v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>59</v>
+      </c>
+      <c r="F51" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("jcpenney.svg",""), </v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>60</v>
+      </c>
+      <c r="F52" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("kohl_s.svg",""), </v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>61</v>
+      </c>
+      <c r="F53" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("dillard_s.svg",""), </v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>62</v>
+      </c>
+      <c r="F54" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("carter_s.svg",""), </v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>63</v>
+      </c>
+      <c r="F55" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("pampers.svg",""), </v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>64</v>
+      </c>
+      <c r="F56" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">new LogoInfo("macy_s.svg",""), </v>
       </c>
     </row>
   </sheetData>
